--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -810,27 +810,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129402882</v>
+        <v>129405959</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,22 +841,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Nrk</t>
+          <t>Bergfallet, Bergfallet, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465172</v>
+        <v>465192</v>
       </c>
       <c r="R3" t="n">
-        <v>6548684</v>
+        <v>6549035</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,24 +907,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,27 +927,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129405959</v>
+        <v>129402882</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -978,22 +958,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallet, Bergfallet, Nrk</t>
+          <t>Kvarntorp, Kvarntorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465192</v>
+        <v>465172</v>
       </c>
       <c r="R4" t="n">
-        <v>6549035</v>
+        <v>6548684</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,9 +1029,24 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -810,27 +810,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129405959</v>
+        <v>129402882</v>
       </c>
       <c r="B3" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,22 +841,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergfallet, Bergfallet, Nrk</t>
+          <t>Kvarntorp, Kvarntorp, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465192</v>
+        <v>465172</v>
       </c>
       <c r="R3" t="n">
-        <v>6549035</v>
+        <v>6548684</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,9 +912,24 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,27 +947,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129402882</v>
+        <v>129405959</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,22 +978,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Nrk</t>
+          <t>Bergfallet, Bergfallet, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465172</v>
+        <v>465192</v>
       </c>
       <c r="R4" t="n">
-        <v>6548684</v>
+        <v>6549035</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,24 +1044,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1062,6 +1062,848 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129599485</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack med intorkat savflöde.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129599979</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465221</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548638</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack i död tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129597341</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6549028</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129598938</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465145</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6548726</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129596773</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>465212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6549150</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack i liggande död trädstam.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129597879</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>465143</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6548959</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack i tall. Delvis med torkat savflöde.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129599485</v>
+        <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,16 +1075,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465200</v>
+        <v>465221</v>
       </c>
       <c r="R5" t="n">
-        <v>6548635</v>
+        <v>6548638</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack med intorkat savflöde.</t>
+          <t>Hack i död tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129599979</v>
+        <v>129597341</v>
       </c>
       <c r="B6" t="n">
         <v>57724</v>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465221</v>
+        <v>465150</v>
       </c>
       <c r="R6" t="n">
-        <v>6548638</v>
+        <v>6549028</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack i död tall.</t>
+          <t>Färska hack i död gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597341</v>
+        <v>129596773</v>
       </c>
       <c r="B7" t="n">
         <v>57724</v>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465150</v>
+        <v>465212</v>
       </c>
       <c r="R7" t="n">
-        <v>6549028</v>
+        <v>6549150</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack i död gran.</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,24 +1455,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1632,10 +1622,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596773</v>
+        <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1643,16 +1633,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1661,21 +1651,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465212</v>
+        <v>465200</v>
       </c>
       <c r="R9" t="n">
-        <v>6549150</v>
+        <v>6548635</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1707,7 +1700,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1717,12 +1710,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack med intorkat savflöde.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,14 +1732,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1793,11 +1796,14 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,113 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129632130</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57854</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>465216</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6548959</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129408524</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>129402882</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>129405959</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129597341</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129596773</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129597879</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>129632130</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -810,27 +810,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129402882</v>
+        <v>129405959</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>58100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,22 +841,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Nrk</t>
+          <t>Bergfallet, Bergfallet, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465172</v>
+        <v>465192</v>
       </c>
       <c r="R3" t="n">
-        <v>6548684</v>
+        <v>6549035</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,24 +907,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,27 +927,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129405959</v>
+        <v>129402882</v>
       </c>
       <c r="B4" t="n">
-        <v>58100</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -978,22 +958,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallet, Bergfallet, Nrk</t>
+          <t>Kvarntorp, Kvarntorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465192</v>
+        <v>465172</v>
       </c>
       <c r="R4" t="n">
-        <v>6549035</v>
+        <v>6548684</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1022,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,9 +1029,24 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129408524</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>129405959</v>
       </c>
       <c r="B3" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>129402882</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129597341</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129596773</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129597879</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>129632130</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129408524</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,27 +810,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129405959</v>
+        <v>129402882</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,22 +841,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergfallet, Bergfallet, Nrk</t>
+          <t>Kvarntorp, Kvarntorp, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465192</v>
+        <v>465172</v>
       </c>
       <c r="R3" t="n">
-        <v>6549035</v>
+        <v>6548684</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,9 +912,24 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,27 +947,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129402882</v>
+        <v>129405959</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,22 +978,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Nrk</t>
+          <t>Bergfallet, Bergfallet, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465172</v>
+        <v>465192</v>
       </c>
       <c r="R4" t="n">
-        <v>6548684</v>
+        <v>6549035</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,24 +1044,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129597341</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596773</v>
+        <v>129598938</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465212</v>
+        <v>465145</v>
       </c>
       <c r="R7" t="n">
-        <v>6549150</v>
+        <v>6548726</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,14 +1455,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1480,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598938</v>
+        <v>129596773</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,16 +1501,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1511,7 +1521,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1520,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465145</v>
+        <v>465212</v>
       </c>
       <c r="R8" t="n">
-        <v>6548726</v>
+        <v>6549150</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1587,24 +1597,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1625,7 +1625,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129597879</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>129632130</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129598938</v>
+        <v>129596773</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465145</v>
+        <v>465212</v>
       </c>
       <c r="R7" t="n">
-        <v>6548726</v>
+        <v>6549150</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,24 +1455,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1490,10 +1480,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596773</v>
+        <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,16 +1491,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1521,7 +1511,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1530,13 +1520,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465212</v>
+        <v>465145</v>
       </c>
       <c r="R8" t="n">
-        <v>6549150</v>
+        <v>6548726</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,14 +1587,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596773</v>
+        <v>129598938</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465212</v>
+        <v>465145</v>
       </c>
       <c r="R7" t="n">
-        <v>6549150</v>
+        <v>6548726</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,14 +1455,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1480,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598938</v>
+        <v>129596773</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,16 +1501,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1511,7 +1521,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1520,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465145</v>
+        <v>465212</v>
       </c>
       <c r="R8" t="n">
-        <v>6548726</v>
+        <v>6549150</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1587,24 +1597,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129597341</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129596773</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129597879</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>129599979</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>129597341</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129596773</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129597879</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>129632130</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596773</v>
+        <v>129598938</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,16 +1359,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1379,7 +1379,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465212</v>
+        <v>465145</v>
       </c>
       <c r="R7" t="n">
-        <v>6549150</v>
+        <v>6548726</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,14 +1455,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1480,10 +1490,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129598938</v>
+        <v>129596773</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,16 +1501,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1511,7 +1521,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1520,13 +1530,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465145</v>
+        <v>465212</v>
       </c>
       <c r="R8" t="n">
-        <v>6548726</v>
+        <v>6549150</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1565,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1575,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1587,24 +1597,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129408524</v>
+        <v>129596773</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,27 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465215</v>
+        <v>465212</v>
       </c>
       <c r="R2" t="n">
-        <v>6548579</v>
+        <v>6549150</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack i liggande död trädstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +782,14 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,27 +807,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129402882</v>
+        <v>129597341</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,19 +838,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarntorp, Kvarntorp, Nrk</t>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465172</v>
+        <v>465150</v>
       </c>
       <c r="R3" t="n">
-        <v>6548684</v>
+        <v>6549028</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -880,27 +877,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska hack i död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,24 +909,29 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +949,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129405959</v>
+        <v>129599979</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,16 +960,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -978,22 +980,22 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallet, Bergfallet, Nrk</t>
+          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465192</v>
+        <v>465221</v>
       </c>
       <c r="R4" t="n">
-        <v>6549035</v>
+        <v>6548638</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,22 +1019,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack i död tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1054,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1064,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129599979</v>
+        <v>129402882</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,16 +1102,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1095,22 +1122,22 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+          <t>Kvarntorp, Kvarntorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465221</v>
+        <v>465172</v>
       </c>
       <c r="R5" t="n">
-        <v>6548638</v>
+        <v>6548684</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,27 +1161,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack i död tall.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,11 +1193,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1183,12 +1205,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,10 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129597341</v>
+        <v>129408524</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,16 +1239,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1235,24 +1257,27 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465150</v>
+        <v>465215</v>
       </c>
       <c r="R6" t="n">
-        <v>6549028</v>
+        <v>6548579</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,27 +1301,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack i död gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,22 +1330,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,10 +1363,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129598938</v>
+        <v>129597879</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,24 +1392,27 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465145</v>
+        <v>465143</v>
       </c>
       <c r="R7" t="n">
-        <v>6548726</v>
+        <v>6548959</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1441,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1451,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack i tall. Delvis med torkat savflöde.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1490,10 +1508,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596773</v>
+        <v>129598938</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,16 +1519,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1521,7 +1539,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1530,13 +1548,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465212</v>
+        <v>465145</v>
       </c>
       <c r="R8" t="n">
-        <v>6549150</v>
+        <v>6548726</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1583,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,12 +1593,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack i liggande död trädstam.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1597,14 +1615,24 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1625,7 +1653,7 @@
         <v>129599485</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1767,27 +1795,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597879</v>
+        <v>129405959</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1796,27 +1824,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slättåsen, Atlasruta 10E0d (Letälven), Nrk</t>
+          <t>Bergfallet, Bergfallet, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465143</v>
+        <v>465192</v>
       </c>
       <c r="R10" t="n">
-        <v>6548959</v>
+        <v>6549035</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1840,27 +1865,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack i tall. Delvis med torkat savflöde.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,26 +1895,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1915,11 +1915,11 @@
         <v>129632130</v>
       </c>
       <c r="B11" t="n">
-        <v>57866</v>
+        <v>58082</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">

--- a/artfynd/A 47975-2025 artfynd.xlsx
+++ b/artfynd/A 47975-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -946,6 +956,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1088,6 +1103,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129599979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1225,6 +1245,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129402882</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1360,6 +1385,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129408524</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1505,6 +1535,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1647,6 +1682,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129598938</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1792,6 +1832,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129599485</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1909,6 +1954,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129405959</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2016,8 +2066,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129632130</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>